--- a/data/review/gpt-5.4-pro/tiebreak/step-4-answers-tiebreak.xlsx
+++ b/data/review/gpt-5.4-pro/tiebreak/step-4-answers-tiebreak.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -435,6 +435,7 @@
     <col width="40" customWidth="1" min="13" max="13"/>
     <col width="40" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -511,6 +512,11 @@
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Agreement</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Reviewer</t>
         </is>
       </c>
     </row>
